--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691553</v>
+        <v>122691474</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>92110</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577469</v>
+        <v>577471</v>
       </c>
       <c r="R2" t="n">
-        <v>6433672</v>
+        <v>6433685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,12 +764,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -785,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691474</v>
+        <v>122691597</v>
       </c>
       <c r="B3" t="n">
-        <v>92110</v>
+        <v>57754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,38 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +838,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577471</v>
+        <v>577478</v>
       </c>
       <c r="R3" t="n">
-        <v>6433685</v>
+        <v>6433643</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,18 +876,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1014,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691416</v>
+        <v>122691553</v>
       </c>
       <c r="B5" t="n">
-        <v>57537</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1026,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577500</v>
+        <v>577469</v>
       </c>
       <c r="R5" t="n">
-        <v>6433555</v>
+        <v>6433672</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B6" t="n">
-        <v>57754</v>
+        <v>57537</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,31 +1132,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R6" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691474</v>
+        <v>122691416</v>
       </c>
       <c r="B2" t="n">
-        <v>92110</v>
+        <v>57537</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577471</v>
+        <v>577500</v>
       </c>
       <c r="R2" t="n">
-        <v>6433685</v>
+        <v>6433555</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,18 +765,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691597</v>
+        <v>122691492</v>
       </c>
       <c r="B3" t="n">
-        <v>57754</v>
+        <v>92118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,27 +805,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577478</v>
+        <v>577523</v>
       </c>
       <c r="R3" t="n">
-        <v>6433643</v>
+        <v>6433644</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691492</v>
+        <v>122691553</v>
       </c>
       <c r="B4" t="n">
-        <v>92118</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,34 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577523</v>
+        <v>577469</v>
       </c>
       <c r="R4" t="n">
-        <v>6433644</v>
+        <v>6433672</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +991,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691553</v>
+        <v>122691597</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>57754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1046,11 +1045,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,13 +1053,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577469</v>
+        <v>577478</v>
       </c>
       <c r="R5" t="n">
-        <v>6433672</v>
+        <v>6433643</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691416</v>
+        <v>122691474</v>
       </c>
       <c r="B6" t="n">
-        <v>57537</v>
+        <v>92110</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,35 +1131,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1166,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577500</v>
+        <v>577471</v>
       </c>
       <c r="R6" t="n">
-        <v>6433555</v>
+        <v>6433685</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,12 +1204,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691416</v>
+        <v>122691484</v>
       </c>
       <c r="B2" t="n">
-        <v>57537</v>
+        <v>92221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577500</v>
+        <v>577523</v>
       </c>
       <c r="R2" t="n">
-        <v>6433555</v>
+        <v>6433644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691492</v>
+        <v>122691597</v>
       </c>
       <c r="B3" t="n">
-        <v>92118</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,30 +805,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577523</v>
+        <v>577478</v>
       </c>
       <c r="R3" t="n">
-        <v>6433644</v>
+        <v>6433643</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +877,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +898,7 @@
         <v>122691553</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1009,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B5" t="n">
-        <v>57754</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,31 +1017,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R5" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1118,7 +1122,7 @@
         <v>122691474</v>
       </c>
       <c r="B6" t="n">
-        <v>92110</v>
+        <v>92213</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691484</v>
+        <v>122691597</v>
       </c>
       <c r="B2" t="n">
-        <v>92221</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577523</v>
+        <v>577478</v>
       </c>
       <c r="R2" t="n">
-        <v>6433644</v>
+        <v>6433643</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,7 +763,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691597</v>
+        <v>122691474</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>92217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577478</v>
+        <v>577471</v>
       </c>
       <c r="R3" t="n">
-        <v>6433643</v>
+        <v>6433685</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,12 +870,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691553</v>
+        <v>122691492</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,35 +912,34 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577469</v>
+        <v>577523</v>
       </c>
       <c r="R4" t="n">
-        <v>6433672</v>
+        <v>6433644</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,6 +991,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691416</v>
+        <v>122691553</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,33 +1026,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577500</v>
+        <v>577469</v>
       </c>
       <c r="R5" t="n">
-        <v>6433555</v>
+        <v>6433672</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691474</v>
+        <v>122691416</v>
       </c>
       <c r="B6" t="n">
-        <v>92213</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,34 +1136,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577471</v>
+        <v>577500</v>
       </c>
       <c r="R6" t="n">
-        <v>6433685</v>
+        <v>6433555</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,18 +1210,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R2" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -781,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691474</v>
+        <v>122691553</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +805,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -832,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577471</v>
+        <v>577469</v>
       </c>
       <c r="R3" t="n">
-        <v>6433685</v>
+        <v>6433672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,18 +875,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691553</v>
+        <v>122691474</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>92217</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,31 +1025,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577469</v>
+        <v>577471</v>
       </c>
       <c r="R5" t="n">
-        <v>6433672</v>
+        <v>6433685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,12 +1098,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1120,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691416</v>
+        <v>122691597</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,39 +1140,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577500</v>
+        <v>577478</v>
       </c>
       <c r="R6" t="n">
-        <v>6433555</v>
+        <v>6433643</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691553</v>
+        <v>122691474</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>92217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577469</v>
+        <v>577471</v>
       </c>
       <c r="R3" t="n">
-        <v>6433672</v>
+        <v>6433685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +878,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691492</v>
+        <v>122691597</v>
       </c>
       <c r="B4" t="n">
-        <v>92225</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +924,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577523</v>
+        <v>577478</v>
       </c>
       <c r="R4" t="n">
-        <v>6433644</v>
+        <v>6433643</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691474</v>
+        <v>122691553</v>
       </c>
       <c r="B5" t="n">
-        <v>92217</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,34 +1030,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577471</v>
+        <v>577469</v>
       </c>
       <c r="R5" t="n">
-        <v>6433685</v>
+        <v>6433672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,18 +1100,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1128,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691597</v>
+        <v>122691484</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>92225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,27 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577478</v>
+        <v>577523</v>
       </c>
       <c r="R6" t="n">
-        <v>6433643</v>
+        <v>6433644</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691416</v>
+        <v>122691474</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>92217</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577500</v>
+        <v>577471</v>
       </c>
       <c r="R2" t="n">
-        <v>6433555</v>
+        <v>6433685</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,12 +764,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691474</v>
+        <v>122691416</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,34 +810,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +846,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577471</v>
+        <v>577500</v>
       </c>
       <c r="R3" t="n">
-        <v>6433685</v>
+        <v>6433555</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,18 +884,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691474</v>
+        <v>122691416</v>
       </c>
       <c r="B2" t="n">
-        <v>92217</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577471</v>
+        <v>577500</v>
       </c>
       <c r="R2" t="n">
-        <v>6433685</v>
+        <v>6433555</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,18 +765,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691416</v>
+        <v>122691474</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>92217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,35 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -846,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577500</v>
+        <v>577471</v>
       </c>
       <c r="R3" t="n">
-        <v>6433555</v>
+        <v>6433685</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,12 +878,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691416</v>
+        <v>122691492</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>92225</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577500</v>
+        <v>577523</v>
       </c>
       <c r="R2" t="n">
-        <v>6433555</v>
+        <v>6433644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +766,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691474</v>
+        <v>122691597</v>
       </c>
       <c r="B3" t="n">
-        <v>92217</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,38 +797,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -840,13 +829,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577471</v>
+        <v>577478</v>
       </c>
       <c r="R3" t="n">
-        <v>6433685</v>
+        <v>6433643</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,18 +867,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -908,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +903,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R4" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1124,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691484</v>
+        <v>122691474</v>
       </c>
       <c r="B6" t="n">
-        <v>92225</v>
+        <v>92217</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,30 +1127,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577523</v>
+        <v>577471</v>
       </c>
       <c r="R6" t="n">
-        <v>6433644</v>
+        <v>6433685</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,6 +1202,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>ca</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,31 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R3" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691416</v>
+        <v>122691597</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,39 +911,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577500</v>
+        <v>577478</v>
       </c>
       <c r="R4" t="n">
-        <v>6433555</v>
+        <v>6433643</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691492</v>
+        <v>122691474</v>
       </c>
       <c r="B2" t="n">
         <v>92225</v>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577523</v>
+        <v>577471</v>
       </c>
       <c r="R2" t="n">
-        <v>6433644</v>
+        <v>6433685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,6 +762,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691416</v>
+        <v>122691553</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,33 +810,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577500</v>
+        <v>577469</v>
       </c>
       <c r="R3" t="n">
-        <v>6433555</v>
+        <v>6433672</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +916,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R4" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691553</v>
+        <v>122691484</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>92233</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,35 +1030,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577469</v>
+        <v>577523</v>
       </c>
       <c r="R5" t="n">
-        <v>6433672</v>
+        <v>6433644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,6 +1113,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1115,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691474</v>
+        <v>122691597</v>
       </c>
       <c r="B6" t="n">
-        <v>92217</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,38 +1144,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1166,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577471</v>
+        <v>577478</v>
       </c>
       <c r="R6" t="n">
-        <v>6433685</v>
+        <v>6433643</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1204,18 +1214,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691474</v>
+        <v>122691416</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577471</v>
+        <v>577500</v>
       </c>
       <c r="R2" t="n">
-        <v>6433685</v>
+        <v>6433555</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,18 +765,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691553</v>
+        <v>122691492</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>92233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,35 +801,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -842,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577469</v>
+        <v>577523</v>
       </c>
       <c r="R3" t="n">
-        <v>6433672</v>
+        <v>6433644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,6 +880,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691416</v>
+        <v>122691553</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,33 +915,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577500</v>
+        <v>577469</v>
       </c>
       <c r="R4" t="n">
-        <v>6433555</v>
+        <v>6433672</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691484</v>
+        <v>122691474</v>
       </c>
       <c r="B5" t="n">
-        <v>92233</v>
+        <v>92225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,30 +1021,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1069,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577523</v>
+        <v>577471</v>
       </c>
       <c r="R5" t="n">
-        <v>6433644</v>
+        <v>6433685</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,6 +1096,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-20</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>ca</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691416</v>
+        <v>122691484</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>92233</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577500</v>
+        <v>577523</v>
       </c>
       <c r="R2" t="n">
-        <v>6433555</v>
+        <v>6433644</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691492</v>
+        <v>122691553</v>
       </c>
       <c r="B3" t="n">
-        <v>92233</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,34 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577523</v>
+        <v>577469</v>
       </c>
       <c r="R3" t="n">
-        <v>6433644</v>
+        <v>6433672</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691553</v>
+        <v>122691597</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,11 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577469</v>
+        <v>577478</v>
       </c>
       <c r="R4" t="n">
-        <v>6433672</v>
+        <v>6433643</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1128,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,31 +1136,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R6" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691484</v>
+        <v>122691492</v>
       </c>
       <c r="B2" t="n">
         <v>92233</v>
@@ -708,11 +708,7 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691553</v>
+        <v>122691474</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>92225</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,31 +801,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577469</v>
+        <v>577471</v>
       </c>
       <c r="R3" t="n">
-        <v>6433672</v>
+        <v>6433685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,12 +874,18 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,31 +916,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R4" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691474</v>
+        <v>122691553</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1034,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1056,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577471</v>
+        <v>577469</v>
       </c>
       <c r="R5" t="n">
-        <v>6433685</v>
+        <v>6433672</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,18 +1104,12 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691416</v>
+        <v>122691597</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1136,39 +1140,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577500</v>
+        <v>577478</v>
       </c>
       <c r="R6" t="n">
-        <v>6433555</v>
+        <v>6433643</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,108 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126166189</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skälstorpet, Hyllela, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>577521</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6433636</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -1237,7 +1237,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -883,7 +883,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">

--- a/artfynd/A 5067-2025 artfynd.xlsx
+++ b/artfynd/A 5067-2025 artfynd.xlsx
@@ -675,40 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122691492</v>
+        <v>122691474</v>
       </c>
       <c r="B2" t="n">
-        <v>92233</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -722,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577523</v>
+        <v>577471</v>
       </c>
       <c r="R2" t="n">
-        <v>6433644</v>
+        <v>6433685</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,11 +759,16 @@
           <t>2025-02-20</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
@@ -785,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122691474</v>
+        <v>122691484</v>
       </c>
       <c r="B3" t="n">
-        <v>92225</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,26 +800,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577471</v>
+        <v>577523</v>
       </c>
       <c r="R3" t="n">
-        <v>6433685</v>
+        <v>6433644</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,16 +873,11 @@
           <t>2025-02-20</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ca</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -904,49 +898,40 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122691416</v>
+        <v>122691553</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577500</v>
+        <v>577469</v>
       </c>
       <c r="R4" t="n">
-        <v>6433555</v>
+        <v>6433672</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,32 +1003,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122691553</v>
+        <v>122691597</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1054,11 +1034,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1042,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577469</v>
+        <v>577478</v>
       </c>
       <c r="R5" t="n">
-        <v>6433672</v>
+        <v>6433643</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,43 +1104,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122691597</v>
+        <v>122691416</v>
       </c>
       <c r="B6" t="n">
-        <v>57848</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577478</v>
+        <v>577500</v>
       </c>
       <c r="R6" t="n">
-        <v>6433643</v>
+        <v>6433555</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,7 +1216,7 @@
         <v>126166189</v>
       </c>
       <c r="B7" t="n">
-        <v>97239</v>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
